--- a/tables and figures/methodology/02_Data_Pipelines_and_Threats.xlsx
+++ b/tables and figures/methodology/02_Data_Pipelines_and_Threats.xlsx
@@ -565,7 +565,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -922,7 +922,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1259,7 +1259,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -1537,7 +1537,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -1975,7 +1975,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -2115,7 +2115,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
@@ -3009,7 +3009,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
@@ -3341,7 +3341,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3718,7 +3718,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>

--- a/tables and figures/methodology/02_Data_Pipelines_and_Threats.xlsx
+++ b/tables and figures/methodology/02_Data_Pipelines_and_Threats.xlsx
@@ -58,9 +58,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="000563C1"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <u val="single"/>
     </font>
     <font>
